--- a/docs/OpenCSTL.xlsx
+++ b/docs/OpenCSTL.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spring\Documents\GitHub\OpenCSTL\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/spring/Documents/GitHub/OpenCSTL/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB679CA-B37A-494B-A37F-B426ADBCC392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04332C3E-DD86-934E-B43F-6C3FFC6CE9E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2475" yWindow="2610" windowWidth="34140" windowHeight="18915" xr2:uid="{619C67F7-00F0-4C46-A399-483E9C62B008}"/>
+    <workbookView xWindow="20560" yWindow="780" windowWidth="20580" windowHeight="24940" activeTab="1" xr2:uid="{619C67F7-00F0-4C46-A399-483E9C62B008}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Negative Structure" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="90">
   <si>
     <t>root</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -244,6 +245,118 @@
   </si>
   <si>
     <t>Type size</t>
+  </si>
+  <si>
+    <t>push</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>push_back</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pop_back</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>push_front</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pop_front</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>erase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assign</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>find</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shrink_to_fit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>max_size</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reverse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>empty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>size</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>front</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>back</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>operator [ ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>begin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>end</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rbegin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>top</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>next</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prev</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -251,20 +364,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="\+0;\-0;0"/>
+    <numFmt numFmtId="176" formatCode="\+0;\-0;0"/>
   </numFmts>
   <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -273,6 +386,7 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="KoPubWorld돋움체 Bold"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
@@ -879,19 +993,19 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="4" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1017,6 +1131,21 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1027,21 +1156,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1390,39 +1504,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE06D03-E65E-4121-BF89-D913E6F20D39}">
   <dimension ref="A1:Q15"/>
-  <sheetFormatPr defaultRowHeight="23.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="24"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="39.5703125" style="1" customWidth="1"/>
-    <col min="4" max="14" width="17.140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" style="1" customWidth="1"/>
-    <col min="16" max="17" width="9.5703125" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="24.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="39.5" style="1" customWidth="1"/>
+    <col min="4" max="14" width="17.1640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="11.5" style="1" customWidth="1"/>
+    <col min="16" max="17" width="9.5" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="38.1" customHeight="1">
-      <c r="A1" s="57" t="s">
+    <row r="1" spans="1:17" ht="38" customHeight="1">
+      <c r="A1" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="58"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="61"/>
-    </row>
-    <row r="2" spans="1:17" ht="26.1" customHeight="1">
+      <c r="B1" s="54"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="57"/>
+    </row>
+    <row r="2" spans="1:17" ht="26" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>38</v>
       </c>
@@ -1443,17 +1557,17 @@
       <c r="L2" s="52"/>
       <c r="M2" s="52"/>
       <c r="N2" s="52"/>
-      <c r="O2" s="53" t="s">
+      <c r="O2" s="58" t="s">
         <v>56</v>
       </c>
       <c r="P2" s="50"/>
-      <c r="Q2" s="54"/>
-    </row>
-    <row r="3" spans="1:17" ht="21.95" customHeight="1">
-      <c r="A3" s="55" t="s">
+      <c r="Q2" s="59"/>
+    </row>
+    <row r="3" spans="1:17" ht="22" customHeight="1">
+      <c r="A3" s="60" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="56"/>
+      <c r="B3" s="61"/>
       <c r="C3" s="7">
         <v>-12</v>
       </c>
@@ -1500,7 +1614,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="21.95" customHeight="1" thickBot="1">
+    <row r="4" spans="1:17" ht="22" customHeight="1" thickBot="1">
       <c r="A4" s="48" t="s">
         <v>58</v>
       </c>
@@ -2050,4 +2164,163 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AC87DB3-A230-F242-9E5F-9DB5A4E5F039}">
+  <dimension ref="A5:B33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="17"/>
+  <sheetData>
+    <row r="5" spans="2:2">
+      <c r="B5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2">
+      <c r="B16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="B17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="B18" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="B19" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="B20" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="B21" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="B22" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="B23" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="B25" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="B27" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="B28" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="B29" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="B30" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="B31" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="B32" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" t="s">
+        <v>89</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>